--- a/Things To Do for Added Scope.xlsx
+++ b/Things To Do for Added Scope.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\ANU\2026\Semester 2\CSC429 Computer Project I\Project\Athi EstateAccessSokoConnectProjectAmalgamated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37912246-C8E3-4D72-B25C-AA41C5A02583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5005DB-6AB2-4F02-9AFD-5BDBA73755FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E558F380-2D54-41DC-9DF9-8458D2901BF9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>The Guiding Principle</t>
   </si>
@@ -1109,6 +1109,9 @@
       </rPr>
       <t xml:space="preserve"> M-Pesa / SMS / Gate</t>
     </r>
+  </si>
+  <si>
+    <t> Time to Build Visitor Pre-Registration</t>
   </si>
 </sst>
 </file>
@@ -1547,78 +1550,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC63C1F7-32EC-4C60-A719-7E868B98E87F}">
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.26953125" customWidth="1"/>
+    <col min="3" max="3" width="48.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="24" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="24" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>

--- a/Things To Do for Added Scope.xlsx
+++ b/Things To Do for Added Scope.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\ANU\2026\Semester 2\CSC429 Computer Project I\Project\Athi EstateAccessSokoConnectProjectAmalgamated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5005DB-6AB2-4F02-9AFD-5BDBA73755FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B16476F-0117-45ED-B2EA-4A9FB24A10CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E558F380-2D54-41DC-9DF9-8458D2901BF9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E558F380-2D54-41DC-9DF9-8458D2901BF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
   <si>
     <t>The Guiding Principle</t>
   </si>
@@ -1112,6 +1113,69 @@
   </si>
   <si>
     <t> Time to Build Visitor Pre-Registration</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Test check-in / check-out</t>
+  </si>
+  <si>
+    <t>5 min</t>
+  </si>
+  <si>
+    <t>Endpoints are built but not clicked through end-to-end</t>
+  </si>
+  <si>
+    <t>SMS via Africa's Talking</t>
+  </si>
+  <si>
+    <t>1–2h</t>
+  </si>
+  <si>
+    <t>Sign up, add credentials, integrate — every email also sends SMS</t>
+  </si>
+  <si>
+    <t>Capacitor mobile wrapper</t>
+  </si>
+  <si>
+    <t>2–4h</t>
+  </si>
+  <si>
+    <t>Installable Android/iOS app from the existing frontend</t>
+  </si>
+  <si>
+    <t>Polish</t>
+  </si>
+  <si>
+    <t>varies</t>
+  </si>
+  <si>
+    <t>HTML email templates, "resend code", bulk actions</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>30 min</t>
+  </si>
+  <si>
+    <t>Update README, clean test data, tag a release</t>
+  </si>
+  <si>
+    <t>Take a break</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Rest; come back later</t>
   </si>
 </sst>
 </file>
@@ -2133,4 +2197,121 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8AEF22F-6F25-492D-9AA6-AEB28829DACE}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="23" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Things To Do for Added Scope.xlsx
+++ b/Things To Do for Added Scope.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\ANU\2026\Semester 2\CSC429 Computer Project I\Project\Athi EstateAccessSokoConnectProjectAmalgamated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B16476F-0117-45ED-B2EA-4A9FB24A10CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39DDE66-F51E-4BDE-8D3A-3F463702C72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E558F380-2D54-41DC-9DF9-8458D2901BF9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{E558F380-2D54-41DC-9DF9-8458D2901BF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="257">
   <si>
     <t>The Guiding Principle</t>
   </si>
@@ -1176,13 +1178,600 @@
   </si>
   <si>
     <t>Rest; come back later</t>
+  </si>
+  <si>
+    <t>__</t>
+  </si>
+  <si>
+    <t>🎯 What's Not Built Yet</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>USSD menu</t>
+  </si>
+  <si>
+    <t>❌ Not started</t>
+  </si>
+  <si>
+    <t>WhatsApp Business API</t>
+  </si>
+  <si>
+    <t>Two-Way SMS (shortcodes)</t>
+  </si>
+  <si>
+    <t>SMS to admin/security notifications</t>
+  </si>
+  <si>
+    <t>❌ Not scoped</t>
+  </si>
+  <si>
+    <t>❌ Deferred</t>
+  </si>
+  <si>
+    <t>Production SMS Sender ID registration</t>
+  </si>
+  <si>
+    <t>❌ Not applied</t>
+  </si>
+  <si>
+    <t>House-number seed for all residents</t>
+  </si>
+  <si>
+    <t>⏳ Partially done</t>
+  </si>
+  <si>
+    <t>Cron for monthly invoice generation</t>
+  </si>
+  <si>
+    <t>❌ Not automated</t>
+  </si>
+  <si>
+    <t>Visitor expiry cron</t>
+  </si>
+  <si>
+    <t>⏳ Endpoint exists, no scheduler</t>
+  </si>
+  <si>
+    <t>🎯 My Honest Take</t>
+  </si>
+  <si>
+    <r>
+      <t>You've built a full-featured estate management portal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with:</t>
+    </r>
+  </si>
+  <si>
+    <t>A complete billing system (with real payment reconciliation workflow)</t>
+  </si>
+  <si>
+    <t>A complete visitor pre-registration system (with 2-stage approval, dual-channel delivery, gate workflow)</t>
+  </si>
+  <si>
+    <t>Admin/security/resident dashboards</t>
+  </si>
+  <si>
+    <t>Real email + SMS integration</t>
+  </si>
+  <si>
+    <t>Proper audit trails</t>
+  </si>
+  <si>
+    <r>
+      <t>This is production-ready for a small-to-medium estate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> as soon as you:</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Register a production Sender ID with Safaricom (~KES 8,700 + 2-5 days)</t>
+  </si>
+  <si>
+    <t>2. Top up Africa's Talking (~KES 500-1000/month for moderate use)</t>
+  </si>
+  <si>
+    <t>3. Finish assigning house numbers to all residents</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The USSD, WhatsApp, and Capacitor work is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>expansion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, not "fixing something broken."</t>
+    </r>
+  </si>
+  <si>
+    <t>🎯 Recommendation</t>
+  </si>
+  <si>
+    <r>
+      <t>Push now.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Lock in the milestone:</t>
+    </r>
+  </si>
+  <si>
+    <t>Three Common Welfare Models</t>
+  </si>
+  <si>
+    <t>Model A — Welfare Fund with Contributions</t>
+  </si>
+  <si>
+    <t>Residents contribute a fixed monthly amount (e.g., KSh 500) to a communal welfare fund. The fund pays out for pre-defined events.</t>
+  </si>
+  <si>
+    <t>Typical features:</t>
+  </si>
+  <si>
+    <t>Fixed monthly contribution amount</t>
+  </si>
+  <si>
+    <t>Every household on record as payer</t>
+  </si>
+  <si>
+    <t>Fund balance visible to all residents</t>
+  </si>
+  <si>
+    <t>Payout when a member experiences an event (death, illness, birth)</t>
+  </si>
+  <si>
+    <t>Admin approves payouts</t>
+  </si>
+  <si>
+    <t>Model B — Welfare Requests + Peer Donations</t>
+  </si>
+  <si>
+    <t>Residents post requests ("Help needed for X"), and other residents contribute individually (not through a fixed fund).</t>
+  </si>
+  <si>
+    <t>Resident creates a welfare request with description + target amount</t>
+  </si>
+  <si>
+    <t>Other residents pledge/contribute via M-Pesa</t>
+  </si>
+  <si>
+    <t>Progress bar showing how much has been raised</t>
+  </si>
+  <si>
+    <t>Admin verifies contributions</t>
+  </si>
+  <si>
+    <t>Request closes when target reached or expired</t>
+  </si>
+  <si>
+    <t>Model C — Both</t>
+  </si>
+  <si>
+    <t>A monthly contribution fund (Model A) + special case requests (Model B).</t>
+  </si>
+  <si>
+    <t>🎯 Typical Welfare Workflow (Model A)</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>1. Resident registers for welfare → agrees to KSh X/month</t>
+  </si>
+  <si>
+    <t>2. Monthly contributions tracked (same as billing)</t>
+  </si>
+  <si>
+    <t>3. Resident experiences qualifying event → submits request</t>
+  </si>
+  <si>
+    <t>4. Admin reviews request → approves or denies</t>
+  </si>
+  <si>
+    <t>5. Approved payout deducted from fund</t>
+  </si>
+  <si>
+    <t>6. All residents see ledger of fund balance + payouts</t>
+  </si>
+  <si>
+    <t>🎯 Questions Before I Design</t>
+  </si>
+  <si>
+    <t>I need six answers to build the right thing.</t>
+  </si>
+  <si>
+    <t>1 — Which model?</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — Fixed monthly contributions + fund payouts</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — Open requests + peer donations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — Both</t>
+    </r>
+  </si>
+  <si>
+    <t>2 — Contribution amount</t>
+  </si>
+  <si>
+    <t>Fixed amount? (e.g., KSh 500/month) → admin-configurable like the KSh 2,000 billing</t>
+  </si>
+  <si>
+    <t>Or member-decided per request (Model B)?</t>
+  </si>
+  <si>
+    <t>3 — Who can request payouts?</t>
+  </si>
+  <si>
+    <t>Any registered resident</t>
+  </si>
+  <si>
+    <t>Only residents who've paid for N months</t>
+  </si>
+  <si>
+    <t>Any household, one request at a time</t>
+  </si>
+  <si>
+    <t>4 — Approval flow</t>
+  </si>
+  <si>
+    <t>Single admin approval</t>
+  </si>
+  <si>
+    <t>Two-stage like visitors (admin → committee)</t>
+  </si>
+  <si>
+    <t>Auto-approve if criteria met</t>
+  </si>
+  <si>
+    <t>5 — Fund accounting</t>
+  </si>
+  <si>
+    <r>
+      <t>Only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> contributions in</t>
+    </r>
+  </si>
+  <si>
+    <t>Contributions + external donations</t>
+  </si>
+  <si>
+    <t>Interest/adjustments manual by admin</t>
+  </si>
+  <si>
+    <t>6 — Visibility</t>
+  </si>
+  <si>
+    <t>All residents see full ledger (open book)</t>
+  </si>
+  <si>
+    <t>Only own contributions</t>
+  </si>
+  <si>
+    <t>Only totals visible, individual amounts private</t>
+  </si>
+  <si>
+    <t>🎯 Database Sketch (Model A — for context)</t>
+  </si>
+  <si>
+    <t>Once you pick a model, we'd add tables like:</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>welfare_members</t>
+  </si>
+  <si>
+    <t>Which residents opted into welfare</t>
+  </si>
+  <si>
+    <t>welfare_contributions</t>
+  </si>
+  <si>
+    <t>Monthly contributions per member</t>
+  </si>
+  <si>
+    <t>welfare_requests</t>
+  </si>
+  <si>
+    <t>Payout requests from residents</t>
+  </si>
+  <si>
+    <t>welfare_payouts</t>
+  </si>
+  <si>
+    <t>Approved payouts (deducted from fund)</t>
+  </si>
+  <si>
+    <t>welfare_ledger</t>
+  </si>
+  <si>
+    <t>Full audit: contrib + payout + balance</t>
+  </si>
+  <si>
+    <t>welfare_settings</t>
+  </si>
+  <si>
+    <t>Monthly amount, event types, rules</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Then a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>welfare.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> page for residents and a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>admin-welfare.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> page for admins.</t>
+    </r>
+  </si>
+  <si>
+    <t>🎯 What I'd Recommend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given how you've structured the estate (billing per household, admin approval workflow), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Model C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> fits best:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Monthly contribution</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (like your KSh 2,000 billing — same invoice pattern)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Open requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for special cases (large funeral, medical emergency)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Two-stage approval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for payouts (admin → committee, or admin → security lead)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Open ledger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> so everyone trusts the fund</t>
+    </r>
+  </si>
+  <si>
+    <t>📋 Just Reply With</t>
+  </si>
+  <si>
+    <t>1. Model: A / B / C</t>
+  </si>
+  <si>
+    <t>2. Amount: &lt;number&gt; (or "member-decided")</t>
+  </si>
+  <si>
+    <t>3. Request eligibility: any resident / N months paid / other</t>
+  </si>
+  <si>
+    <t>4. Approval: single admin / two-stage / auto</t>
+  </si>
+  <si>
+    <t>5. Fund sources: contributions only / + donations / + other</t>
+  </si>
+  <si>
+    <t>6. Visibility: full ledger / private / totals only</t>
+  </si>
+  <si>
+    <t>Example:</t>
+  </si>
+  <si>
+    <t>1. C</t>
+  </si>
+  <si>
+    <t>2. 500</t>
+  </si>
+  <si>
+    <t>3. any registered resident</t>
+  </si>
+  <si>
+    <t>4. two-stage</t>
+  </si>
+  <si>
+    <t>5. contributions only</t>
+  </si>
+  <si>
+    <t>6. full ledger</t>
+  </si>
+  <si>
+    <r>
+      <t>Once I have those six, I'll design the schema and ship the welfare module the same way we did billing and visitors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — DB → routes → admin page → resident page.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>What's your setup?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 🚀</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1241,6 +1830,24 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1262,7 +1869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1299,6 +1906,33 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2201,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8AEF22F-6F25-492D-9AA6-AEB28829DACE}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" customWidth="1"/>
@@ -2311,6 +2945,640 @@
         <v>134</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F07EA1-D5A8-442F-819E-81EE6BA93257}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="38.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="38.453125" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="23" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="23" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="23" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445B9C6B-78F0-499B-88C1-764AB2DABAAB}">
+  <dimension ref="A1:B91"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="112" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="161" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="92" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="92" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="172.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="69" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="112" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="149.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="184" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="115" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="115" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="126.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="32" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="132" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="46" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="48" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="115" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="64" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="230" x14ac:dyDescent="0.35">
+      <c r="A37" s="17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="115" x14ac:dyDescent="0.35">
+      <c r="A38" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="80" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="103.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="92" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="48" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="69" x14ac:dyDescent="0.35">
+      <c r="A44" s="17" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="115" x14ac:dyDescent="0.35">
+      <c r="A45" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="64" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="46" x14ac:dyDescent="0.35">
+      <c r="A48" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="17" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="92" x14ac:dyDescent="0.35">
+      <c r="A50" s="17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="32" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="115" x14ac:dyDescent="0.35">
+      <c r="A52" s="17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="115" x14ac:dyDescent="0.35">
+      <c r="A54" s="17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="132" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="46" x14ac:dyDescent="0.35">
+      <c r="A60" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="46" x14ac:dyDescent="0.35">
+      <c r="A61" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="46" x14ac:dyDescent="0.35">
+      <c r="A63" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="120" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="126.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="195.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="20" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="195.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="20" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="207" x14ac:dyDescent="0.35">
+      <c r="A71" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="103.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" s="19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" s="19" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" s="19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="19" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" s="19" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" s="19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" s="19" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="230" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
